--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/LOUISIANA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/LOUISIANA_2012.xlsx
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C65">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C120">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C365">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C402">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C661">
